--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1505,6 +1505,121 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123353712</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>800508</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7177131</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1510,7 +1510,7 @@
         <v>123353712</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1619,6 +1619,916 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123440623</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>800423</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7177160</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123440805</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>800280</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7176970</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>barksprätt på insektsangripen gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123440766</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>800270</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7176986</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123440552</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>800422</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7177151</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123440876</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91244</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>800299</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7176872</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123440710</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>800427</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7177160</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i grann</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123440435</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>800439</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7177151</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska hack i gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123440837</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>800280</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7176969</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440623</v>
+        <v>123440710</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800423</v>
+        <v>800427</v>
       </c>
       <c r="R10" t="n">
         <v>7177160</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>hack i grann</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440805</v>
+        <v>123440435</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800280</v>
+        <v>800439</v>
       </c>
       <c r="R11" t="n">
-        <v>7176970</v>
+        <v>7177151</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>barksprätt på insektsangripen gran</t>
+          <t>färska hack i gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440766</v>
+        <v>123440837</v>
       </c>
       <c r="B12" t="n">
         <v>57497</v>
@@ -1890,7 +1890,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800270</v>
+        <v>800280</v>
       </c>
       <c r="R12" t="n">
-        <v>7176986</v>
+        <v>7176969</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,11 +1936,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2082,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123440876</v>
+        <v>123440623</v>
       </c>
       <c r="B14" t="n">
-        <v>91244</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,30 +2093,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2129,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800299</v>
+        <v>800423</v>
       </c>
       <c r="R14" t="n">
-        <v>7176872</v>
+        <v>7177160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,13 +2163,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440710</v>
+        <v>123440766</v>
       </c>
       <c r="B15" t="n">
         <v>57497</v>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800427</v>
+        <v>800270</v>
       </c>
       <c r="R15" t="n">
-        <v>7177160</v>
+        <v>7176986</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i grann</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440435</v>
+        <v>123440876</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>91244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,31 +2323,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2355,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800439</v>
+        <v>800299</v>
       </c>
       <c r="R16" t="n">
-        <v>7177151</v>
+        <v>7176872</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2393,17 +2392,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>färska hack i gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2422,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440837</v>
+        <v>123440805</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,16 +2433,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2460,7 +2455,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2473,7 +2468,7 @@
         <v>800280</v>
       </c>
       <c r="R17" t="n">
-        <v>7176969</v>
+        <v>7176970</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,6 +2501,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440710</v>
+        <v>123440876</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>91250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,31 +1638,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800427</v>
+        <v>800299</v>
       </c>
       <c r="R10" t="n">
-        <v>7177160</v>
+        <v>7176872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,17 +1707,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>hack i grann</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1737,7 +1732,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440435</v>
+        <v>123440766</v>
       </c>
       <c r="B11" t="n">
         <v>57497</v>
@@ -1775,7 +1770,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800439</v>
+        <v>800270</v>
       </c>
       <c r="R11" t="n">
-        <v>7177151</v>
+        <v>7176986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska hack i gran</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440837</v>
+        <v>123440552</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,16 +1863,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1890,7 +1885,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1900,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800280</v>
+        <v>800422</v>
       </c>
       <c r="R12" t="n">
-        <v>7176969</v>
+        <v>7177151</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,6 +1931,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,7 +1962,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123440552</v>
+        <v>123440805</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800422</v>
+        <v>800280</v>
       </c>
       <c r="R13" t="n">
-        <v>7177151</v>
+        <v>7176970</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123440623</v>
+        <v>123440435</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,16 +2093,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2115,7 +2115,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800423</v>
+        <v>800439</v>
       </c>
       <c r="R14" t="n">
-        <v>7177160</v>
+        <v>7177151</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>färska hack i gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440766</v>
+        <v>123440710</v>
       </c>
       <c r="B15" t="n">
         <v>57497</v>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800270</v>
+        <v>800427</v>
       </c>
       <c r="R15" t="n">
-        <v>7176986</v>
+        <v>7177160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>hack i grann</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440876</v>
+        <v>123440837</v>
       </c>
       <c r="B16" t="n">
-        <v>91244</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,30 +2323,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2354,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800299</v>
+        <v>800280</v>
       </c>
       <c r="R16" t="n">
-        <v>7176872</v>
+        <v>7176969</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,7 +2399,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440805</v>
+        <v>123440623</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2455,7 +2455,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800280</v>
+        <v>800423</v>
       </c>
       <c r="R17" t="n">
-        <v>7176970</v>
+        <v>7177160</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>barksprätt på insektsangripen gran</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440876</v>
+        <v>123440837</v>
       </c>
       <c r="B10" t="n">
-        <v>91250</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,30 +1638,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1669,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800299</v>
+        <v>800280</v>
       </c>
       <c r="R10" t="n">
-        <v>7176872</v>
+        <v>7176969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,7 +1714,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440766</v>
+        <v>123440876</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>91253</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,31 +1748,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1780,10 +1779,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800270</v>
+        <v>800299</v>
       </c>
       <c r="R11" t="n">
-        <v>7176986</v>
+        <v>7176872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,17 +1817,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1847,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440552</v>
+        <v>123440766</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,16 +1858,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1885,7 +1880,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1895,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800422</v>
+        <v>800270</v>
       </c>
       <c r="R12" t="n">
-        <v>7177151</v>
+        <v>7176986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1930,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,7 +1957,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123440805</v>
+        <v>123440623</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -2000,7 +1995,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2010,10 +2005,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800280</v>
+        <v>800423</v>
       </c>
       <c r="R13" t="n">
-        <v>7176970</v>
+        <v>7177160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,7 +2045,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>barksprätt på insektsangripen gran</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123440435</v>
+        <v>123440805</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,16 +2088,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2125,10 +2120,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800439</v>
+        <v>800280</v>
       </c>
       <c r="R14" t="n">
-        <v>7177151</v>
+        <v>7176970</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2160,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska hack i gran</t>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2307,7 +2302,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440837</v>
+        <v>123440435</v>
       </c>
       <c r="B16" t="n">
         <v>57497</v>
@@ -2345,7 +2340,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2355,10 +2350,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800280</v>
+        <v>800439</v>
       </c>
       <c r="R16" t="n">
-        <v>7176969</v>
+        <v>7177151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,6 +2386,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska hack i gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,7 +2417,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440623</v>
+        <v>123440552</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2455,7 +2455,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800423</v>
+        <v>800422</v>
       </c>
       <c r="R17" t="n">
-        <v>7177160</v>
+        <v>7177151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1510,7 +1510,7 @@
         <v>123353712</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440837</v>
+        <v>123440623</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800280</v>
+        <v>800423</v>
       </c>
       <c r="R10" t="n">
-        <v>7176969</v>
+        <v>7177160</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,6 +1706,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,7 +1740,7 @@
         <v>123440876</v>
       </c>
       <c r="B11" t="n">
-        <v>91253</v>
+        <v>91270</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1845,7 +1850,7 @@
         <v>123440766</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123440623</v>
+        <v>123440710</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,16 +1978,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2005,7 +2010,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800423</v>
+        <v>800427</v>
       </c>
       <c r="R13" t="n">
         <v>7177160</v>
@@ -2045,7 +2050,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>hack i grann</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123440805</v>
+        <v>123440435</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,16 +2093,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2120,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800280</v>
+        <v>800439</v>
       </c>
       <c r="R14" t="n">
-        <v>7176970</v>
+        <v>7177151</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2165,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>barksprätt på insektsangripen gran</t>
+          <t>färska hack i gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440710</v>
+        <v>123440552</v>
       </c>
       <c r="B15" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,16 +2208,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2225,7 +2230,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2235,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800427</v>
+        <v>800422</v>
       </c>
       <c r="R15" t="n">
-        <v>7177160</v>
+        <v>7177151</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2275,7 +2280,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i grann</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440435</v>
+        <v>123440805</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,16 +2323,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2350,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800439</v>
+        <v>800280</v>
       </c>
       <c r="R16" t="n">
-        <v>7177151</v>
+        <v>7176970</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2395,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska hack i gran</t>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,10 +2422,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440552</v>
+        <v>123440837</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>57503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2433,16 +2438,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2455,7 +2460,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2465,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800422</v>
+        <v>800280</v>
       </c>
       <c r="R17" t="n">
-        <v>7177151</v>
+        <v>7176969</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2501,11 +2506,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1737,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440876</v>
+        <v>123440766</v>
       </c>
       <c r="B11" t="n">
-        <v>91270</v>
+        <v>57503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,30 +1753,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1784,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800299</v>
+        <v>800270</v>
       </c>
       <c r="R11" t="n">
-        <v>7176872</v>
+        <v>7176986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,13 +1823,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1847,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440766</v>
+        <v>123440876</v>
       </c>
       <c r="B12" t="n">
-        <v>57503</v>
+        <v>91270</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,31 +1868,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1895,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800270</v>
+        <v>800299</v>
       </c>
       <c r="R12" t="n">
-        <v>7176986</v>
+        <v>7176872</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,17 +1937,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1510,7 +1510,7 @@
         <v>123353712</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440623</v>
+        <v>123440805</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800423</v>
+        <v>800280</v>
       </c>
       <c r="R10" t="n">
-        <v>7177160</v>
+        <v>7176970</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440766</v>
+        <v>123440876</v>
       </c>
       <c r="B11" t="n">
-        <v>57503</v>
+        <v>91275</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,31 +1753,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1785,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800270</v>
+        <v>800299</v>
       </c>
       <c r="R11" t="n">
-        <v>7176986</v>
+        <v>7176872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,17 +1822,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1852,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440876</v>
+        <v>123440837</v>
       </c>
       <c r="B12" t="n">
-        <v>91270</v>
+        <v>57506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,30 +1863,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1899,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800299</v>
+        <v>800280</v>
       </c>
       <c r="R12" t="n">
-        <v>7176872</v>
+        <v>7176969</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,7 +1939,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1965,7 +1960,7 @@
         <v>123440710</v>
       </c>
       <c r="B13" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         <v>123440435</v>
       </c>
       <c r="B14" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2192,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440552</v>
+        <v>123440623</v>
       </c>
       <c r="B15" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,7 +2225,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2240,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800422</v>
+        <v>800423</v>
       </c>
       <c r="R15" t="n">
-        <v>7177151</v>
+        <v>7177160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2275,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440805</v>
+        <v>123440766</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57506</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,16 +2318,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2345,7 +2340,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2355,10 +2350,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800280</v>
+        <v>800270</v>
       </c>
       <c r="R16" t="n">
-        <v>7176970</v>
+        <v>7176986</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,7 +2390,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>barksprätt på insektsangripen gran</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440837</v>
+        <v>123440552</v>
       </c>
       <c r="B17" t="n">
-        <v>57503</v>
+        <v>57490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,16 +2433,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2460,7 +2455,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2470,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800280</v>
+        <v>800422</v>
       </c>
       <c r="R17" t="n">
-        <v>7176969</v>
+        <v>7177151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,6 +2501,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1510,7 +1510,7 @@
         <v>123353712</v>
       </c>
       <c r="B9" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440805</v>
+        <v>123440710</v>
       </c>
       <c r="B10" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800280</v>
+        <v>800427</v>
       </c>
       <c r="R10" t="n">
-        <v>7176970</v>
+        <v>7177160</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>barksprätt på insektsangripen gran</t>
+          <t>hack i grann</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,7 +1740,7 @@
         <v>123440876</v>
       </c>
       <c r="B11" t="n">
-        <v>91275</v>
+        <v>91277</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440837</v>
+        <v>123440805</v>
       </c>
       <c r="B12" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
         <v>800280</v>
       </c>
       <c r="R12" t="n">
-        <v>7176969</v>
+        <v>7176970</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,6 +1931,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123440710</v>
+        <v>123440435</v>
       </c>
       <c r="B13" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,7 +2000,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2005,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800427</v>
+        <v>800439</v>
       </c>
       <c r="R13" t="n">
-        <v>7177160</v>
+        <v>7177151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2050,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hack i grann</t>
+          <t>färska hack i gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123440435</v>
+        <v>123440766</v>
       </c>
       <c r="B14" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,7 +2115,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2120,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800439</v>
+        <v>800270</v>
       </c>
       <c r="R14" t="n">
-        <v>7177151</v>
+        <v>7176986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2165,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska hack i gran</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440623</v>
+        <v>123440552</v>
       </c>
       <c r="B15" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,7 +2230,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2235,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800423</v>
+        <v>800422</v>
       </c>
       <c r="R15" t="n">
-        <v>7177160</v>
+        <v>7177151</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2275,7 +2280,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440766</v>
+        <v>123440623</v>
       </c>
       <c r="B16" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,16 +2323,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2350,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800270</v>
+        <v>800423</v>
       </c>
       <c r="R16" t="n">
-        <v>7176986</v>
+        <v>7177160</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2395,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,10 +2422,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440552</v>
+        <v>123440837</v>
       </c>
       <c r="B17" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2433,16 +2438,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2455,7 +2460,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2465,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800422</v>
+        <v>800280</v>
       </c>
       <c r="R17" t="n">
-        <v>7177151</v>
+        <v>7176969</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2501,11 +2506,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1622,7 +1622,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440710</v>
+        <v>123440837</v>
       </c>
       <c r="B10" t="n">
         <v>57507</v>
@@ -1660,7 +1660,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800427</v>
+        <v>800280</v>
       </c>
       <c r="R10" t="n">
-        <v>7177160</v>
+        <v>7176969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,11 +1706,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>hack i grann</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440876</v>
+        <v>123440710</v>
       </c>
       <c r="B11" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,30 +1748,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1784,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800299</v>
+        <v>800427</v>
       </c>
       <c r="R11" t="n">
-        <v>7176872</v>
+        <v>7177160</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,13 +1818,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hack i grann</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440805</v>
+        <v>123440623</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1885,7 +1885,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800280</v>
+        <v>800423</v>
       </c>
       <c r="R12" t="n">
-        <v>7176970</v>
+        <v>7177160</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>barksprätt på insektsangripen gran</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123440435</v>
+        <v>123440876</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>91277</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,31 +1978,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2010,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800439</v>
+        <v>800299</v>
       </c>
       <c r="R13" t="n">
-        <v>7177151</v>
+        <v>7176872</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,17 +2047,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska hack i gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2192,7 +2187,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440552</v>
+        <v>123440805</v>
       </c>
       <c r="B15" t="n">
         <v>57491</v>
@@ -2240,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800422</v>
+        <v>800280</v>
       </c>
       <c r="R15" t="n">
-        <v>7177151</v>
+        <v>7176970</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2275,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,7 +2302,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440623</v>
+        <v>123440552</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2345,7 +2340,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2355,10 +2350,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800423</v>
+        <v>800422</v>
       </c>
       <c r="R16" t="n">
-        <v>7177160</v>
+        <v>7177151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,7 +2390,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,7 +2417,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440837</v>
+        <v>123440435</v>
       </c>
       <c r="B17" t="n">
         <v>57507</v>
@@ -2460,7 +2455,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2470,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800280</v>
+        <v>800439</v>
       </c>
       <c r="R17" t="n">
-        <v>7176969</v>
+        <v>7177151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,6 +2501,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska hack i gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440837</v>
+        <v>123440623</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800280</v>
+        <v>800423</v>
       </c>
       <c r="R10" t="n">
-        <v>7176969</v>
+        <v>7177160</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,6 +1706,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440710</v>
+        <v>123440552</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,16 +1753,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1770,7 +1775,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800427</v>
+        <v>800422</v>
       </c>
       <c r="R11" t="n">
-        <v>7177160</v>
+        <v>7177151</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>hack i grann</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440623</v>
+        <v>123440710</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,16 +1868,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1895,7 +1900,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800423</v>
+        <v>800427</v>
       </c>
       <c r="R12" t="n">
         <v>7177160</v>
@@ -1935,7 +1940,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>hack i grann</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123440876</v>
+        <v>123440435</v>
       </c>
       <c r="B13" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,30 +1983,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2009,10 +2015,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800299</v>
+        <v>800439</v>
       </c>
       <c r="R13" t="n">
-        <v>7176872</v>
+        <v>7177151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,13 +2053,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska hack i gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2072,7 +2082,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123440766</v>
+        <v>123440837</v>
       </c>
       <c r="B14" t="n">
         <v>57507</v>
@@ -2110,7 +2120,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2120,10 +2130,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800270</v>
+        <v>800280</v>
       </c>
       <c r="R14" t="n">
-        <v>7176986</v>
+        <v>7176969</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,11 +2166,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440805</v>
+        <v>123440766</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,16 +2208,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2225,7 +2230,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2235,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800280</v>
+        <v>800270</v>
       </c>
       <c r="R15" t="n">
-        <v>7176970</v>
+        <v>7176986</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2275,7 +2280,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>barksprätt på insektsangripen gran</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440552</v>
+        <v>123440876</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>91277</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,31 +2323,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2350,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800422</v>
+        <v>800299</v>
       </c>
       <c r="R16" t="n">
-        <v>7177151</v>
+        <v>7176872</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2388,17 +2392,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440435</v>
+        <v>123440805</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2433,16 +2433,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800439</v>
+        <v>800280</v>
       </c>
       <c r="R17" t="n">
-        <v>7177151</v>
+        <v>7176970</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska hack i gran</t>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440623</v>
+        <v>123440876</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>91277</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,31 +1638,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800423</v>
+        <v>800299</v>
       </c>
       <c r="R10" t="n">
-        <v>7177160</v>
+        <v>7176872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,17 +1707,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack på gammal gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1737,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440552</v>
+        <v>123440435</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,16 +1748,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1785,7 +1780,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800422</v>
+        <v>800439</v>
       </c>
       <c r="R11" t="n">
         <v>7177151</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>färska hack i gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123440435</v>
+        <v>123440552</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,16 +1978,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2015,7 +2010,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800439</v>
+        <v>800422</v>
       </c>
       <c r="R13" t="n">
         <v>7177151</v>
@@ -2055,7 +2050,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>färska hack i gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123440837</v>
+        <v>123440805</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,16 +2093,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2120,7 +2115,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2133,7 +2128,7 @@
         <v>800280</v>
       </c>
       <c r="R14" t="n">
-        <v>7176969</v>
+        <v>7176970</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,6 +2161,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440766</v>
+        <v>123440623</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800270</v>
+        <v>800423</v>
       </c>
       <c r="R15" t="n">
-        <v>7176986</v>
+        <v>7177160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440876</v>
+        <v>123440766</v>
       </c>
       <c r="B16" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,30 +2323,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2354,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800299</v>
+        <v>800270</v>
       </c>
       <c r="R16" t="n">
-        <v>7176872</v>
+        <v>7176986</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2392,13 +2393,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2417,10 +2422,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440805</v>
+        <v>123440837</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2433,16 +2438,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2455,7 +2460,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2468,7 +2473,7 @@
         <v>800280</v>
       </c>
       <c r="R17" t="n">
-        <v>7176970</v>
+        <v>7176969</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2501,11 +2506,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440876</v>
+        <v>123440766</v>
       </c>
       <c r="B10" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,30 +1638,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1669,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800299</v>
+        <v>800270</v>
       </c>
       <c r="R10" t="n">
-        <v>7176872</v>
+        <v>7176986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,13 +1708,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1732,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440435</v>
+        <v>123440552</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,16 +1753,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1780,7 +1785,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800439</v>
+        <v>800422</v>
       </c>
       <c r="R11" t="n">
         <v>7177151</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska hack i gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440710</v>
+        <v>123440805</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,16 +1868,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1885,7 +1890,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1895,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800427</v>
+        <v>800280</v>
       </c>
       <c r="R12" t="n">
-        <v>7177160</v>
+        <v>7176970</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1940,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>hack i grann</t>
+          <t>barksprätt på insektsangripen gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123440552</v>
+        <v>123440837</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,16 +1983,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2000,7 +2005,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2010,10 +2015,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800422</v>
+        <v>800280</v>
       </c>
       <c r="R13" t="n">
-        <v>7177151</v>
+        <v>7176969</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,11 +2051,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123440805</v>
+        <v>123440710</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,16 +2093,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2115,7 +2115,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800280</v>
+        <v>800427</v>
       </c>
       <c r="R14" t="n">
-        <v>7176970</v>
+        <v>7177160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>barksprätt på insektsangripen gran</t>
+          <t>hack i grann</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440623</v>
+        <v>123440435</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2230,7 +2230,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800423</v>
+        <v>800439</v>
       </c>
       <c r="R15" t="n">
-        <v>7177160</v>
+        <v>7177151</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>färska hack i gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440766</v>
+        <v>123440623</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,16 +2323,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800270</v>
+        <v>800423</v>
       </c>
       <c r="R16" t="n">
-        <v>7176986</v>
+        <v>7177160</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,10 +2422,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440837</v>
+        <v>123440876</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>91277</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,31 +2438,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2470,10 +2469,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800280</v>
+        <v>800299</v>
       </c>
       <c r="R17" t="n">
-        <v>7176969</v>
+        <v>7176872</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2514,6 +2513,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1737,7 +1737,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440552</v>
+        <v>123440623</v>
       </c>
       <c r="B11" t="n">
         <v>57491</v>
@@ -1775,7 +1775,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800422</v>
+        <v>800423</v>
       </c>
       <c r="R11" t="n">
-        <v>7177151</v>
+        <v>7177160</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440805</v>
+        <v>123440876</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>91277</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,31 +1868,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1900,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800280</v>
+        <v>800299</v>
       </c>
       <c r="R12" t="n">
-        <v>7176970</v>
+        <v>7176872</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,17 +1937,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>barksprätt på insektsangripen gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123440837</v>
+        <v>123440552</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,16 +1978,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2005,7 +2000,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2015,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800280</v>
+        <v>800422</v>
       </c>
       <c r="R13" t="n">
-        <v>7176969</v>
+        <v>7177151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,6 +2046,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,7 +2077,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123440710</v>
+        <v>123440837</v>
       </c>
       <c r="B14" t="n">
         <v>57507</v>
@@ -2115,7 +2115,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800427</v>
+        <v>800280</v>
       </c>
       <c r="R14" t="n">
-        <v>7177160</v>
+        <v>7176969</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,11 +2161,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>hack i grann</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,7 +2187,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123440435</v>
+        <v>123440710</v>
       </c>
       <c r="B15" t="n">
         <v>57507</v>
@@ -2230,7 +2225,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2240,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800439</v>
+        <v>800427</v>
       </c>
       <c r="R15" t="n">
-        <v>7177151</v>
+        <v>7177160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2275,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska hack i gran</t>
+          <t>hack i grann</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123440623</v>
+        <v>123440435</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,16 +2318,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2345,7 +2340,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2355,10 +2350,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800423</v>
+        <v>800439</v>
       </c>
       <c r="R16" t="n">
-        <v>7177160</v>
+        <v>7177151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,7 +2390,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>färska hack i gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123440876</v>
+        <v>123440805</v>
       </c>
       <c r="B17" t="n">
-        <v>91277</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,30 +2433,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2469,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800299</v>
+        <v>800280</v>
       </c>
       <c r="R17" t="n">
-        <v>7176872</v>
+        <v>7176970</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,13 +2503,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>barksprätt på insektsangripen gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>123440552</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>123440805</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 30834-2020 artfynd.xlsx
+++ b/artfynd/A 30834-2020 artfynd.xlsx
@@ -1967,11 +1967,6 @@
       <c r="B13" t="n">
         <v>57635</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2081,11 +2076,6 @@
       </c>
       <c r="B14" t="n">
         <v>57635</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
